--- a/one-off scripts/variable_analysis_res_hist_full.xlsx
+++ b/one-off scripts/variable_analysis_res_hist_full.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://zhaw-my.sharepoint.com/personal/hedd_zhaw_ch/Documents/Dashboard Squarefoot Projekt/Squarefoot/Squarefoot code/squarefoot/one-off scripts/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="330" documentId="11_E0A39FCD8F79A8D366075C52F37BD2723A439CDF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3EC77299-517D-4A59-ADD0-E3933438C9DE}"/>
+  <xr:revisionPtr revIDLastSave="332" documentId="11_E0A39FCD8F79A8D366075C52F37BD2723A439CDF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2DDC1136-5BD0-4243-97EB-8D20CDD5848E}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="360" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -280,7 +280,7 @@
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -1146,10 +1146,6 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1440,31 +1436,31 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.28515625" customWidth="1"/>
-    <col min="2" max="2" width="25.42578125" customWidth="1"/>
-    <col min="3" max="3" width="26.85546875" customWidth="1"/>
-    <col min="4" max="4" width="26.42578125" customWidth="1"/>
-    <col min="5" max="5" width="43.140625" customWidth="1"/>
-    <col min="6" max="6" width="35.140625" customWidth="1"/>
+    <col min="1" max="1" width="18.33203125" customWidth="1"/>
+    <col min="2" max="2" width="25.44140625" customWidth="1"/>
+    <col min="3" max="3" width="26.88671875" customWidth="1"/>
+    <col min="4" max="4" width="26.44140625" customWidth="1"/>
+    <col min="5" max="5" width="43.109375" customWidth="1"/>
+    <col min="6" max="6" width="35.109375" customWidth="1"/>
     <col min="7" max="7" width="28" customWidth="1"/>
-    <col min="8" max="8" width="21.5703125" customWidth="1"/>
-    <col min="9" max="9" width="23.140625" customWidth="1"/>
-    <col min="10" max="10" width="24.140625" customWidth="1"/>
-    <col min="11" max="11" width="21.42578125" customWidth="1"/>
-    <col min="12" max="12" width="22.42578125" customWidth="1"/>
-    <col min="13" max="13" width="23.5703125" customWidth="1"/>
-    <col min="14" max="14" width="22.140625" customWidth="1"/>
-    <col min="15" max="15" width="25.7109375" customWidth="1"/>
-    <col min="16" max="16" width="26.5703125" customWidth="1"/>
-    <col min="17" max="17" width="42.28515625" customWidth="1"/>
-    <col min="18" max="18" width="23.85546875" customWidth="1"/>
-    <col min="19" max="19" width="25.85546875" customWidth="1"/>
-    <col min="20" max="20" width="26.85546875" customWidth="1"/>
+    <col min="8" max="8" width="21.5546875" customWidth="1"/>
+    <col min="9" max="9" width="23.109375" customWidth="1"/>
+    <col min="10" max="10" width="24.109375" customWidth="1"/>
+    <col min="11" max="11" width="21.44140625" customWidth="1"/>
+    <col min="12" max="12" width="22.44140625" customWidth="1"/>
+    <col min="13" max="13" width="23.5546875" customWidth="1"/>
+    <col min="14" max="14" width="22.109375" customWidth="1"/>
+    <col min="15" max="15" width="25.6640625" customWidth="1"/>
+    <col min="16" max="16" width="26.5546875" customWidth="1"/>
+    <col min="17" max="17" width="42.33203125" customWidth="1"/>
+    <col min="18" max="18" width="23.88671875" customWidth="1"/>
+    <col min="19" max="19" width="25.88671875" customWidth="1"/>
+    <col min="20" max="20" width="26.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1523,7 +1519,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>39</v>
       </c>
@@ -1582,7 +1578,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="3" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
         <v>19</v>
       </c>
@@ -1644,7 +1640,7 @@
         <v>0.25209728599999998</v>
       </c>
     </row>
-    <row r="4" spans="1:20" s="20" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:20" s="20" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="19" t="s">
         <v>20</v>
       </c>
@@ -1706,69 +1702,69 @@
         <v>0.36849241700000002</v>
       </c>
     </row>
-    <row r="5" spans="1:20" s="20" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="19" t="s">
+    <row r="5" spans="1:20" s="6" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="20">
+      <c r="B5" s="6">
         <v>11</v>
       </c>
-      <c r="C5" s="20">
+      <c r="C5" s="6">
         <v>0.18065560350000001</v>
       </c>
-      <c r="D5" s="20">
+      <c r="D5" s="6">
         <v>6.3659074499999996E-2</v>
       </c>
-      <c r="E5" s="20">
+      <c r="E5" s="6">
         <v>6.6683399749999997E-2</v>
       </c>
-      <c r="F5" s="20">
+      <c r="F5" s="6">
         <v>5.8461553999999999E-2</v>
       </c>
-      <c r="G5" s="20">
+      <c r="G5" s="6">
         <v>5.7702135250000001E-2</v>
       </c>
-      <c r="H5" s="20">
+      <c r="H5" s="6">
         <v>2.5633449097500001</v>
       </c>
-      <c r="I5" s="20">
+      <c r="I5" s="6">
         <v>2.4705719300000002</v>
       </c>
-      <c r="J5" s="20">
+      <c r="J5" s="6">
         <v>2.8757342697500001</v>
       </c>
-      <c r="K5" s="20">
+      <c r="K5" s="6">
         <v>2.84435504575</v>
       </c>
-      <c r="L5" s="20">
+      <c r="L5" s="6">
         <v>3.5584619609999999</v>
       </c>
-      <c r="M5" s="20">
+      <c r="M5" s="6">
         <v>2.5356836880000002</v>
       </c>
-      <c r="N5" s="20">
+      <c r="N5" s="6">
         <v>2.1822124172500001</v>
       </c>
-      <c r="O5" s="20">
+      <c r="O5" s="6">
         <v>22.745065437499999</v>
       </c>
-      <c r="P5" s="20">
+      <c r="P5" s="6">
         <v>37.877941634999999</v>
       </c>
-      <c r="Q5" s="20">
+      <c r="Q5" s="6">
         <v>0</v>
       </c>
-      <c r="R5" s="20">
+      <c r="R5" s="6">
         <v>0.28949953350000002</v>
       </c>
-      <c r="S5" s="20">
+      <c r="S5" s="6">
         <v>0.12710524049999999</v>
       </c>
-      <c r="T5" s="20">
+      <c r="T5" s="6">
         <v>0.37612690425</v>
       </c>
     </row>
-    <row r="6" spans="1:20" s="6" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:20" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>22</v>
       </c>
@@ -1830,7 +1826,7 @@
         <v>0.40041762819999999</v>
       </c>
     </row>
-    <row r="7" spans="1:20" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:20" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
         <v>23</v>
       </c>
@@ -1892,7 +1888,7 @@
         <v>0.41172854949999999</v>
       </c>
     </row>
-    <row r="8" spans="1:20" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="10" t="s">
         <v>24</v>
       </c>
@@ -1954,7 +1950,7 @@
         <v>0.42098524089891698</v>
       </c>
     </row>
-    <row r="9" spans="1:20" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:20" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
         <v>25</v>
       </c>
@@ -2016,69 +2012,69 @@
         <v>0.42545152879999998</v>
       </c>
     </row>
-    <row r="10" spans="1:20" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="8" t="s">
+    <row r="10" spans="1:20" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="3">
+      <c r="B10" s="4">
         <v>21.475000000000001</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="4">
         <v>0.26093171074999999</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="4">
         <v>8.79067075E-2</v>
       </c>
-      <c r="E10" s="3">
+      <c r="E10" s="4">
         <v>9.7219735500000001E-2</v>
       </c>
-      <c r="F10" s="3">
+      <c r="F10" s="4">
         <v>8.6867260750000008E-2</v>
       </c>
-      <c r="G10" s="3">
+      <c r="G10" s="4">
         <v>8.5740648500000002E-2</v>
       </c>
-      <c r="H10" s="3">
+      <c r="H10" s="4">
         <v>3.3742794757499999</v>
       </c>
-      <c r="I10" s="3">
+      <c r="I10" s="4">
         <v>3.48504541975</v>
       </c>
-      <c r="J10" s="3">
+      <c r="J10" s="4">
         <v>3.2652780809999999</v>
       </c>
-      <c r="K10" s="3">
+      <c r="K10" s="4">
         <v>3.2321411697500002</v>
       </c>
-      <c r="L10" s="3">
+      <c r="L10" s="4">
         <v>3.8420479570000001</v>
       </c>
-      <c r="M10" s="3">
+      <c r="M10" s="4">
         <v>3.7041566234999999</v>
       </c>
-      <c r="N10" s="3">
+      <c r="N10" s="4">
         <v>2.9280467557500001</v>
       </c>
-      <c r="O10" s="3">
+      <c r="O10" s="4">
         <v>54.995062052500003</v>
       </c>
-      <c r="P10" s="3">
+      <c r="P10" s="4">
         <v>67.263057689999997</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="Q10" s="4">
         <v>9.6678690299999985</v>
       </c>
-      <c r="R10" s="3">
+      <c r="R10" s="4">
         <v>0.42623034274999999</v>
       </c>
-      <c r="S10" s="3">
+      <c r="S10" s="4">
         <v>0.31730836899999998</v>
       </c>
-      <c r="T10" s="3">
+      <c r="T10" s="4">
         <v>0.45640332275000001</v>
       </c>
     </row>
-    <row r="11" spans="1:20" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:20" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
         <v>27</v>
       </c>
@@ -2140,7 +2136,7 @@
         <v>0.46673236359999998</v>
       </c>
     </row>
-    <row r="12" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
         <v>28</v>
       </c>
@@ -2202,7 +2198,7 @@
         <v>0.92386845399999995</v>
       </c>
     </row>
-    <row r="13" spans="1:20" s="22" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:20" s="22" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A13" s="21" t="s">
         <v>29</v>
       </c>
@@ -2264,17 +2260,17 @@
         <v>9.8239946600000017E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:20" ht="191.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:20" ht="191.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:20" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:20" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A16" s="8" t="s">
         <v>34</v>
       </c>
@@ -2336,7 +2332,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="17" spans="1:20" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:20" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17" s="9" t="s">
         <v>33</v>
       </c>
@@ -2398,12 +2394,12 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="18" spans="1:20" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:20" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A18" s="10" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="19" spans="1:20" s="20" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:20" s="20" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A19" s="19" t="s">
         <v>35</v>
       </c>
@@ -2465,7 +2461,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="20" spans="1:20" s="18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:20" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A20" s="17" t="s">
         <v>36</v>
       </c>
@@ -2527,10 +2523,10 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A21" s="12"/>
     </row>
-    <row r="24" spans="1:20" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:20" s="14" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A24" s="13" t="s">
         <v>41</v>
       </c>
@@ -2592,7 +2588,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="25" spans="1:20" s="16" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:20" s="16" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A25" s="15" t="s">
         <v>32</v>
       </c>
@@ -2654,7 +2650,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="26" spans="1:20" s="18" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:20" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A26" s="17" t="s">
         <v>40</v>
       </c>
